--- a/artfynd/A 31887-2024 artfynd.xlsx
+++ b/artfynd/A 31887-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119746253</v>
+        <v>119745936</v>
       </c>
       <c r="B2" t="n">
         <v>90562</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587520</v>
+        <v>587522</v>
       </c>
       <c r="R2" t="n">
-        <v>6963550</v>
+        <v>6963537</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119746478</v>
+        <v>119745715</v>
       </c>
       <c r="B3" t="n">
         <v>90527</v>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rödmyran, Rödmyran, Mpd</t>
+          <t>Hattberget, Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587578</v>
+        <v>587543</v>
       </c>
       <c r="R3" t="n">
-        <v>6963424</v>
+        <v>6963541</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119745609</v>
+        <v>119746478</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hattberget, Hattberget, Mpd</t>
+          <t>Rödmyran, Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587535</v>
+        <v>587578</v>
       </c>
       <c r="R4" t="n">
-        <v>6963567</v>
+        <v>6963424</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119745936</v>
+        <v>119746253</v>
       </c>
       <c r="B5" t="n">
         <v>90562</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587522</v>
+        <v>587520</v>
       </c>
       <c r="R5" t="n">
-        <v>6963537</v>
+        <v>6963550</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119746642</v>
+        <v>119745609</v>
       </c>
       <c r="B6" t="n">
-        <v>96862</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587513</v>
+        <v>587535</v>
       </c>
       <c r="R6" t="n">
-        <v>6963470</v>
+        <v>6963567</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119745715</v>
+        <v>119746642</v>
       </c>
       <c r="B8" t="n">
-        <v>90527</v>
+        <v>96862</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587543</v>
+        <v>587513</v>
       </c>
       <c r="R8" t="n">
-        <v>6963541</v>
+        <v>6963470</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 31887-2024 artfynd.xlsx
+++ b/artfynd/A 31887-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119745936</v>
+        <v>119745715</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587522</v>
+        <v>587543</v>
       </c>
       <c r="R2" t="n">
-        <v>6963537</v>
+        <v>6963541</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119745715</v>
+        <v>119745936</v>
       </c>
       <c r="B3" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587543</v>
+        <v>587522</v>
       </c>
       <c r="R3" t="n">
-        <v>6963541</v>
+        <v>6963537</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119746478</v>
+        <v>119746092</v>
       </c>
       <c r="B4" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rödmyran, Rödmyran, Mpd</t>
+          <t>Hattberget, Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587578</v>
+        <v>587512</v>
       </c>
       <c r="R4" t="n">
-        <v>6963424</v>
+        <v>6963524</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119746253</v>
+        <v>119746478</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +997,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hattberget, Hattberget, Mpd</t>
+          <t>Rödmyran, Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587520</v>
+        <v>587578</v>
       </c>
       <c r="R5" t="n">
-        <v>6963550</v>
+        <v>6963424</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119745609</v>
+        <v>119746118</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1099,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hattberget, Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587535</v>
+        <v>587512</v>
       </c>
       <c r="R6" t="n">
-        <v>6963567</v>
+        <v>6963557</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119746118</v>
+        <v>119745609</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,42 +1205,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hattberget, Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587512</v>
+        <v>587535</v>
       </c>
       <c r="R7" t="n">
-        <v>6963557</v>
+        <v>6963567</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1393,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119746092</v>
+        <v>119746253</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,42 +1409,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hattberget, Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587512</v>
+        <v>587520</v>
       </c>
       <c r="R9" t="n">
-        <v>6963524</v>
+        <v>6963550</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 31887-2024 artfynd.xlsx
+++ b/artfynd/A 31887-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119745715</v>
+        <v>119746118</v>
       </c>
       <c r="B2" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hattberget, Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587543</v>
+        <v>587512</v>
       </c>
       <c r="R2" t="n">
-        <v>6963541</v>
+        <v>6963557</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -879,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119746092</v>
+        <v>119745609</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,42 +895,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hattberget, Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587512</v>
+        <v>587535</v>
       </c>
       <c r="R4" t="n">
-        <v>6963524</v>
+        <v>6963567</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,7 +985,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119746478</v>
+        <v>119745715</v>
       </c>
       <c r="B5" t="n">
         <v>90527</v>
@@ -1021,14 +1021,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rödmyran, Rödmyran, Mpd</t>
+          <t>Hattberget, Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587578</v>
+        <v>587543</v>
       </c>
       <c r="R5" t="n">
-        <v>6963424</v>
+        <v>6963541</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119746118</v>
+        <v>119746478</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,42 +1099,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hattberget, Hattberget, Mpd</t>
+          <t>Rödmyran, Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587512</v>
+        <v>587578</v>
       </c>
       <c r="R6" t="n">
-        <v>6963557</v>
+        <v>6963424</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1193,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119745609</v>
+        <v>119746092</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,38 +1201,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hattberget, Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587535</v>
+        <v>587512</v>
       </c>
       <c r="R7" t="n">
-        <v>6963567</v>
+        <v>6963524</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 31887-2024 artfynd.xlsx
+++ b/artfynd/A 31887-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119746118</v>
+        <v>119745609</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hattberget, Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587512</v>
+        <v>587535</v>
       </c>
       <c r="R2" t="n">
-        <v>6963557</v>
+        <v>6963567</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119745936</v>
+        <v>119746092</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hattberget, Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587522</v>
+        <v>587512</v>
       </c>
       <c r="R3" t="n">
-        <v>6963537</v>
+        <v>6963524</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119745609</v>
+        <v>119745715</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>90545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,25 +895,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587535</v>
+        <v>587543</v>
       </c>
       <c r="R4" t="n">
-        <v>6963567</v>
+        <v>6963541</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119745715</v>
+        <v>119746478</v>
       </c>
       <c r="B5" t="n">
-        <v>90527</v>
+        <v>90545</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,14 +1021,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hattberget, Hattberget, Mpd</t>
+          <t>Rödmyran, Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587543</v>
+        <v>587578</v>
       </c>
       <c r="R5" t="n">
-        <v>6963541</v>
+        <v>6963424</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119746478</v>
+        <v>119746118</v>
       </c>
       <c r="B6" t="n">
-        <v>90527</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,38 +1099,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rödmyran, Rödmyran, Mpd</t>
+          <t>Hattberget, Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587578</v>
+        <v>587512</v>
       </c>
       <c r="R6" t="n">
-        <v>6963424</v>
+        <v>6963557</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1189,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119746092</v>
+        <v>119746642</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>96885</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,42 +1205,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hattberget, Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587512</v>
+        <v>587513</v>
       </c>
       <c r="R7" t="n">
-        <v>6963524</v>
+        <v>6963470</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1295,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119746642</v>
+        <v>119745936</v>
       </c>
       <c r="B8" t="n">
-        <v>96862</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,25 +1307,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587513</v>
+        <v>587522</v>
       </c>
       <c r="R8" t="n">
-        <v>6963470</v>
+        <v>6963537</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1400,7 +1400,7 @@
         <v>119746253</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
